--- a/outputs/267-18.xlsx
+++ b/outputs/267-18.xlsx
@@ -164,12 +164,16 @@
       <protection locked="false" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -177,7 +181,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -189,11 +193,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -457,69 +461,69 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="89.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="17.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="89.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="str">
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="str">
         <f aca="false">CONCATENATE("[","""",E1,"""",", """&amp;I$1&amp;"",A$1,"/",A1,""", """&amp;C1&amp;""", """&amp;A1&amp;"""],")</f>
         <v>["/link/", "path2img&amp;track/path2img&amp;track", "alt-text", "path2img&amp;track"],</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="0" t="s">
+      <c r="H1" s="5"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" s="7" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="str">
+      <c r="F2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7" t="str">
         <f aca="false">CONCATENATE("//[","""",E2,"""",", """&amp;I$1&amp;"",A$1,"/",A2,""", """&amp;C2&amp;""", """&amp;A2&amp;"""],")</f>
         <v>//["/link/", "path2img&amp;track/path2img&amp;track2", "alt-text?", "path2img&amp;track2"],</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="6" t="s">
+      <c r="H2" s="9"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="7" t="s">
         <v>1</v>
       </c>
     </row>

--- a/outputs/267-18.xlsx
+++ b/outputs/267-18.xlsx
@@ -518,7 +518,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="7" t="str">
-        <f aca="false">CONCATENATE("//[","""",E2,"""",", """&amp;I$1&amp;"",A$1,"/",A2,""", """&amp;C2&amp;""", """&amp;A2&amp;"""],")</f>
+        <f aca="false">CONCATENATE("//","[","""",E2,"""",", """&amp;I$1&amp;"",A$1,"/",A2,""", """&amp;C2&amp;""", """&amp;A2&amp;"""],")</f>
         <v>//["/link/", "path2img&amp;track/path2img&amp;track2", "alt-text?", "path2img&amp;track2"],</v>
       </c>
       <c r="H2" s="9"/>
